--- a/artfynd/A 32649-2023 artfynd.xlsx
+++ b/artfynd/A 32649-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32649-2023 artfynd.xlsx
+++ b/artfynd/A 32649-2023 artfynd.xlsx
@@ -675,54 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111618056</v>
+        <v>111618039</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580582.6881743574</v>
+        <v>580600</v>
       </c>
       <c r="R2" t="n">
-        <v>6415124.22061418</v>
+        <v>6415234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,24 +747,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111618039</v>
+        <v>111618046</v>
       </c>
       <c r="B3" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580599.6803078586</v>
+        <v>580592</v>
       </c>
       <c r="R3" t="n">
-        <v>6415233.627682217</v>
+        <v>6415156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,19 +849,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111618144</v>
+        <v>111618056</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,7 +909,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,7 +917,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -978,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580620.6996611424</v>
+        <v>580583</v>
       </c>
       <c r="R4" t="n">
-        <v>6415142.541277731</v>
+        <v>6415124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,19 +963,14 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,42 +998,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111618046</v>
+        <v>111618070</v>
       </c>
       <c r="B5" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1095,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580591.6383206119</v>
+        <v>580592</v>
       </c>
       <c r="R5" t="n">
-        <v>6415156.322361182</v>
+        <v>6415141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,19 +1082,14 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,15 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111618070</v>
+        <v>111618078</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,21 +1145,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580592.470229132</v>
+        <v>580612</v>
       </c>
       <c r="R6" t="n">
-        <v>6415141.442167919</v>
+        <v>6415119</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,24 +1193,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111618078</v>
+        <v>111618089</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,13 +1251,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1350,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580612.1009209087</v>
+        <v>580618</v>
       </c>
       <c r="R7" t="n">
-        <v>6415119.491031807</v>
+        <v>6415137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,19 +1307,14 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,15 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111618089</v>
+        <v>111618109</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1372,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1475,14 +1389,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 32649, Heda, Sm</t>
+          <t>A 32649, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580617.6201989455</v>
+        <v>580619</v>
       </c>
       <c r="R8" t="n">
-        <v>6415136.627037819</v>
+        <v>6415113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,19 +1426,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1557,15 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111618109</v>
+        <v>111618144</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1491,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1600,23 +1499,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 32649, Sm</t>
+          <t>A 32649, Heda, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580619.1666838422</v>
+        <v>580621</v>
       </c>
       <c r="R9" t="n">
-        <v>6415112.716507593</v>
+        <v>6415143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,24 +1541,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD9" t="b">
